--- a/data/trans_camb/P1419-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1419-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -1,06</t>
+          <t>-4,79; -1,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; -0,93</t>
+          <t>-4,45; -1,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,46</t>
+          <t>-0,99; 4,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -0,11</t>
+          <t>-5,96; -0,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -2,74</t>
+          <t>-8,68; -2,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,46</t>
+          <t>-2,52; 3,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; -0,9</t>
+          <t>-4,53; -1,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,33; -2,32</t>
+          <t>-6,13; -2,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,53</t>
+          <t>-0,73; 3,38</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,13; -24,3</t>
+          <t>-74,92; -27,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-73,63; -20,56</t>
+          <t>-73,12; -22,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 105,42</t>
+          <t>-17,29; 95,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,94; -0,42</t>
+          <t>-30,74; -1,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,59; -16,94</t>
+          <t>-46,9; -15,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 22,14</t>
+          <t>-13,16; 21,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,29; -8,38</t>
+          <t>-34,33; -8,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,23; -21,13</t>
+          <t>-47,72; -20,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 31,23</t>
+          <t>-5,34; 29,94</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>2,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,29</t>
+          <t>-2,09; -0,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,24</t>
+          <t>-1,69; 0,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,1</t>
+          <t>0,34; 2,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,01</t>
+          <t>-2,99; 0,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; -0,79</t>
+          <t>-3,88; -0,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,62</t>
+          <t>1,12; 4,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -0,43</t>
+          <t>-2,23; -0,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; -0,62</t>
+          <t>-2,4; -0,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,56</t>
+          <t>1,23; 3,13</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,28; -14,62</t>
+          <t>-78,01; -18,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,99; 20,64</t>
+          <t>-63,14; 7,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 138,38</t>
+          <t>11,34; 157,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 0,45</t>
+          <t>-40,14; 6,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,38; -12,7</t>
+          <t>-51,04; -13,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 64,44</t>
+          <t>14,35; 75,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,38; -11,92</t>
+          <t>-46,49; -12,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,36; -15,78</t>
+          <t>-50,25; -15,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 67,07</t>
+          <t>25,01; 83,67</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; -0,13</t>
+          <t>-3,3; -0,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,5</t>
+          <t>-2,68; 0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,78</t>
+          <t>-1,31; 2,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -0,26</t>
+          <t>-6,05; -0,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -0,66</t>
+          <t>-6,32; -0,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,78</t>
+          <t>-2,37; 3,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -0,73</t>
+          <t>-3,72; -0,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,49</t>
+          <t>-3,52; -0,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,83</t>
+          <t>-0,85; 2,15</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 41,57</t>
+          <t>-100,0; 122,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,27; 52,34</t>
+          <t>-84,91; 84,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,52; 156,34</t>
+          <t>-41,43; 174,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,46; -3,79</t>
+          <t>-75,19; -5,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,21; -11,22</t>
+          <t>-78,45; -9,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,58; 65,03</t>
+          <t>-30,15; 76,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,49; -20,54</t>
+          <t>-76,25; -21,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,54; -15,71</t>
+          <t>-72,53; -11,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 63,14</t>
+          <t>-17,96; 70,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>0,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -1,08</t>
+          <t>-2,65; -1,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; -0,74</t>
+          <t>-2,18; -0,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,38</t>
+          <t>-0,09; 1,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,96</t>
+          <t>-3,81; -0,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,04; -3,13</t>
+          <t>-5,87; -3,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,71</t>
+          <t>-1,29; 1,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -1,28</t>
+          <t>-2,86; -1,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -2,28</t>
+          <t>-3,85; -2,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,77</t>
+          <t>-0,31; 1,33</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-7,27%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,66%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-74,01; -41,66</t>
+          <t>-74,19; -42,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-63,6; -28,6</t>
+          <t>-62,82; -25,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 52,1</t>
+          <t>-2,41; 66,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,33; -9,32</t>
+          <t>-33,15; -9,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,35; -30,91</t>
+          <t>-51,99; -32,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 6,71</t>
+          <t>-11,05; 14,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,54; -19,5</t>
+          <t>-38,83; -19,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,84; -34,54</t>
+          <t>-51,87; -33,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 11,94</t>
+          <t>-4,23; 20,44</t>
         </is>
       </c>
     </row>
